--- a/artfynd/A 70179-2021 artfynd.xlsx
+++ b/artfynd/A 70179-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 70179-2021 artfynd.xlsx
+++ b/artfynd/A 70179-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99802073</v>
+        <v>99802072</v>
       </c>
       <c r="B2" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>653103.5473217713</v>
+        <v>653105</v>
       </c>
       <c r="R2" t="n">
-        <v>7182408.808240815</v>
+        <v>7182387</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-04-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99802072</v>
+        <v>99802071</v>
       </c>
       <c r="B3" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rusbäcken, Rusfors, Lycksele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>653104.6751683478</v>
+        <v>653147</v>
       </c>
       <c r="R3" t="n">
-        <v>7182386.608766365</v>
+        <v>7182290</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +864,9 @@
           <t>2022-04-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,21 +878,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -930,6 +890,122 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>99802073</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rusbäcken, Rusfors, Lycksele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>653104</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7182409</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>

--- a/artfynd/A 70179-2021 artfynd.xlsx
+++ b/artfynd/A 70179-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99802072</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99802071</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,8 +1025,18 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99802073</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>